--- a/csv/model/market share limits/formula_market share limits_BC.xlsx
+++ b/csv/model/market share limits/formula_market share limits_BC.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="33675" yWindow="3075" windowWidth="17280" windowHeight="8475" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3624" yWindow="2148" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" calcOnSave="0"/>
 </workbook>
 </file>
 
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -592,7 +592,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8242,7 +8242,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9667,7 +9667,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -11092,7 +11092,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11767,7 +11767,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11842,7 +11842,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -12217,7 +12217,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -12367,7 +12367,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12592,7 +12592,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12667,7 +12667,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12892,7 +12892,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -13117,7 +13117,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -14317,7 +14317,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14842,7 +14842,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -15142,7 +15142,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -15292,7 +15292,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15442,7 +15442,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15592,7 +15592,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15667,7 +15667,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15817,7 +15817,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15892,7 +15892,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15967,7 +15967,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -16117,7 +16117,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16492,7 +16492,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16642,7 +16642,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16717,7 +16717,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16792,7 +16792,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16867,7 +16867,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16942,7 +16942,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -17167,7 +17167,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -17242,7 +17242,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -17317,7 +17317,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17477,7 +17477,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17562,7 +17562,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17732,7 +17732,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17817,7 +17817,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17902,7 +17902,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17987,7 +17987,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -18412,7 +18412,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -18497,7 +18497,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18667,7 +18667,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18837,7 +18837,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18922,7 +18922,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -19007,7 +19007,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -19177,7 +19177,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -19517,7 +19517,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19857,7 +19857,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -20027,7 +20027,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -20197,7 +20197,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -20282,7 +20282,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -20452,7 +20452,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20877,7 +20877,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20962,7 +20962,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -21047,7 +21047,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -21132,7 +21132,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -21217,7 +21217,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -21302,7 +21302,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -21387,7 +21387,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Market share new_min</t>
+          <t>market_share_new_min</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -21627,7 +21627,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -21717,7 +21717,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -21867,7 +21867,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -21947,7 +21947,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -22027,7 +22027,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -22107,7 +22107,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -22267,7 +22267,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -22347,7 +22347,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -22427,7 +22427,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -22507,7 +22507,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -22587,7 +22587,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -22667,7 +22667,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -22827,7 +22827,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -22987,7 +22987,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -23067,7 +23067,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -23147,7 +23147,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -23307,7 +23307,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -23387,7 +23387,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Market share new_max</t>
+          <t>market_share_new_max</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
